--- a/input/mapping/017. OCB_GOLD_TCKH_V_PLA_NIM_UPL_QUANG.xlsx
+++ b/input/mapping/017. OCB_GOLD_TCKH_V_PLA_NIM_UPL_QUANG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{7AB843C8-A9CB-4B6F-B192-431348CFB4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1B26251-4BF8-4E77-8456-0C53877DBFD4}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{7AB843C8-A9CB-4B6F-B192-431348CFB4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2775A29A-5083-47BD-855A-02B3A14414B2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Script SQL" sheetId="3" r:id="rId2"/>
     <sheet name="V_PLA_NIM_UPL" sheetId="2" r:id="rId3"/>
-    <sheet name="PLA_NIM_UPL" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="67">
   <si>
     <t>V_PLA_NIM_UPL  —  Data Lineage Mind Map</t>
   </si>
@@ -258,60 +257,12 @@
     <t>A.NIM_BQLK * A.SDBQLK
 → Thu thuần lãi = NIM bình quân lũy kế × Số dư bình quân lũy kế</t>
   </si>
-  <si>
-    <t xml:space="preserve">FIELD MAPPING </t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field </t>
-  </si>
-  <si>
-    <t>Data Type</t>
-  </si>
-  <si>
-    <t>Transform Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform Logic </t>
-  </si>
-  <si>
-    <t>datetime</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>nvarchar(255)</t>
-  </si>
-  <si>
-    <t>decimal(20,2)</t>
-  </si>
-  <si>
-    <t>decimal(20,6)</t>
-  </si>
-  <si>
-    <t>UPL_DATE</t>
-  </si>
-  <si>
-    <t>varchar(9)</t>
-  </si>
-  <si>
-    <t>decimal(8,0)</t>
-  </si>
-  <si>
-    <t>nvarchar(50)</t>
-  </si>
-  <si>
-    <t>decimal(24,6)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,28 +343,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color rgb="FF002060"/>
       <name val="Arial"/>
@@ -431,7 +360,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,24 +411,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF974706"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE26B0A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF4D93D9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -523,7 +434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -743,21 +654,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF808080"/>
       </left>
       <right style="thin">
@@ -788,7 +684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -850,18 +746,14 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -871,9 +763,18 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -882,26 +783,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1302,13 +1183,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="7"/>
@@ -1332,62 +1213,62 @@
     </row>
     <row r="4" spans="2:6" ht="15"/>
     <row r="5" spans="2:6" ht="27" customHeight="1">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="32" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B6" s="41"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="43"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="33"/>
     </row>
     <row r="11" spans="2:6" ht="16.5">
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="22"/>
     </row>
     <row r="12" spans="2:6" ht="15">
-      <c r="C12" s="35"/>
-      <c r="D12" s="36" t="s">
+      <c r="C12" s="23"/>
+      <c r="D12" s="24" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="15">
-      <c r="C13" s="37"/>
-      <c r="D13" s="36" t="s">
+      <c r="C13" s="25"/>
+      <c r="D13" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="15">
-      <c r="C14" s="38"/>
-      <c r="D14" s="36" t="s">
+      <c r="C14" s="26"/>
+      <c r="D14" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="15">
-      <c r="C15" s="39"/>
-      <c r="D15" s="36" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15">
-      <c r="C16" s="40"/>
-      <c r="D16" s="36" t="s">
+      <c r="C16" s="28"/>
+      <c r="D16" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1467,13 +1348,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="17" t="s">
@@ -1506,14 +1387,14 @@
       <c r="E3" s="11"/>
     </row>
     <row r="6" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="31"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="38"/>
     </row>
     <row r="7" spans="1:6" ht="30.75">
       <c r="A7" s="19" t="s">
@@ -1844,342 +1725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3024FA-669D-462E-B030-092461CD085A}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="6" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2351,8 +1897,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80CA59F4-E515-4A4B-A5E9-D78EAC6889C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BC741E-ED57-4A4F-BC82-1496C0A9B9AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2360,5 +1925,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BC741E-ED57-4A4F-BC82-1496C0A9B9AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80CA59F4-E515-4A4B-A5E9-D78EAC6889C4}"/>
 </file>